--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -633,7 +633,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -1106,7 +1106,7 @@
     <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
+    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1151,7 +1151,7 @@
 </t>
   </si>
   <si>
-    <t>このobservationが行われるヘルスケアイベント</t>
+    <t>このobservationが行われる診療イベント</t>
   </si>
   <si>
     <t>例：診療、歯科検診、身元不明者調査</t>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>
